--- a/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Regneark_Kapitalbehov.xlsx
+++ b/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Regneark_Kapitalbehov.xlsx
@@ -1192,12 +1192,16 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1205,11 +1209,11 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="6" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1217,7 +1221,7 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1225,15 +1229,15 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="166" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1241,11 +1245,11 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="10" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="167" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1257,31 +1261,31 @@
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1289,59 +1293,59 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="168" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="8" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="169" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="11" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1609,263 +1613,263 @@
   <dimension ref="A1:C32"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="70"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="70"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="2"/>
-      <c r="C2" s="2"/>
+      <c r="B2" s="3"/>
+      <c r="C2" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="4" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="6" t="n">
+      <c r="B5" s="7" t="n">
         <v>850000</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C5" s="8" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="6" t="n">
+      <c r="B6" s="7" t="n">
         <v>480000</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="8" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="B7" s="6" t="n">
+      <c r="B7" s="7" t="n">
         <v>3960000</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C7" s="8" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="B8" s="8" t="n">
+      <c r="B8" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C8" s="7" t="s">
+      <c r="C8" s="8" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="B9" s="6" t="n">
+      <c r="B9" s="7" t="n">
         <v>2250000</v>
       </c>
-      <c r="C9" s="7" t="s">
+      <c r="C9" s="8" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="8" t="n">
+      <c r="B10" s="9" t="n">
         <v>20</v>
       </c>
-      <c r="C10" s="7" t="s">
+      <c r="C10" s="8" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B11" s="6" t="n">
+      <c r="B11" s="7" t="n">
         <v>200000</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C11" s="8" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="B12" s="9" t="n">
+      <c r="B12" s="10" t="n">
         <v>0.3</v>
       </c>
-      <c r="C12" s="7" t="s">
+      <c r="C12" s="8" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="B14" s="4"/>
-      <c r="C14" s="4"/>
+      <c r="B14" s="5"/>
+      <c r="C14" s="5"/>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="B15" s="10" t="n">
+      <c r="B15" s="11" t="n">
         <f aca="false">B5+B6</f>
         <v>1330000</v>
       </c>
-      <c r="C15" s="7" t="s">
+      <c r="C15" s="8" t="s">
         <v>21</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>22</v>
       </c>
-      <c r="B16" s="10" t="n">
+      <c r="B16" s="11" t="n">
         <f aca="false">B7*B8/360</f>
         <v>220000</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="8" t="s">
         <v>23</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="10" t="n">
+      <c r="B17" s="11" t="n">
         <f aca="false">B9*B10/360</f>
         <v>125000</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="8" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="B18" s="10" t="n">
+      <c r="B18" s="11" t="n">
         <f aca="false">B16+B17+B11</f>
         <v>545000</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="8" t="s">
         <v>27</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="20" customFormat="false" ht="21" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="11" t="s">
+      <c r="A20" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="B20" s="12" t="n">
+      <c r="B20" s="13" t="n">
         <f aca="false">B15+B18</f>
         <v>1875000</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="8" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="B21" s="13" t="n">
+      <c r="B21" s="14" t="n">
         <f aca="false">B18/B20</f>
         <v>0.290666666666667</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="8" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="B22" s="10" t="n">
+      <c r="B22" s="11" t="n">
         <f aca="false">B20*B12</f>
         <v>562500</v>
       </c>
-      <c r="C22" s="7" t="s">
+      <c r="C22" s="8" t="s">
         <v>33</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B24" s="4"/>
-      <c r="C24" s="4"/>
+      <c r="B24" s="5"/>
+      <c r="C24" s="5"/>
     </row>
     <row r="25" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="14" t="str">
+      <c r="A25" s="15" t="str">
         <f aca="false">"Bedriften trenger "&amp;TEXT(ROUND(B20,0),"#,##0")&amp;" kroner før den går rundt. "&amp;TEXT(ROUND(B18,0),"#,##0")&amp;" kroner av dem kjøper ingenting. De står og venter på lager, hos kunder og i reserve."</f>
         <v>Bedriften trenger 1,875,000 kroner før den går rundt. 545,000 kroner av dem kjøper ingenting. De står og venter på lager, hos kunder og i reserve.</v>
       </c>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
+      <c r="B25" s="15"/>
+      <c r="C25" s="15"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="4" t="s">
         <v>35</v>
       </c>
-      <c r="B27" s="4"/>
-      <c r="C27" s="4"/>
+      <c r="B27" s="5"/>
+      <c r="C27" s="5"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="15" t="s">
+      <c r="A28" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="B28" s="15"/>
-      <c r="C28" s="15"/>
+      <c r="B28" s="16"/>
+      <c r="C28" s="16"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="15" t="s">
+      <c r="A29" s="16" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="15"/>
-      <c r="C29" s="15"/>
+      <c r="B29" s="16"/>
+      <c r="C29" s="16"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="15" t="s">
+      <c r="A30" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="15"/>
-      <c r="C30" s="15"/>
+      <c r="B30" s="16"/>
+      <c r="C30" s="16"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
     <row r="32" customFormat="false" ht="27" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="2" t="s">
+      <c r="A32" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B32" s="2"/>
-      <c r="C32" s="2"/>
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
     </row>
   </sheetData>
   <mergeCells count="6">
@@ -1894,305 +1898,305 @@
   <dimension ref="A1:C50"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="40"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="62"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="40"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="62"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="17" t="s">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="18" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="19" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="20" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="20" t="s">
+      <c r="B5" s="21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="22" t="s">
         <v>46</v>
       </c>
-      <c r="B6" s="20" t="s">
+      <c r="B6" s="21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="22" t="s">
         <v>48</v>
       </c>
-      <c r="B7" s="20" t="s">
+      <c r="B7" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
         <v>51</v>
       </c>
-      <c r="B10" s="20" t="s">
+      <c r="B10" s="21" t="s">
         <v>52</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="22" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="B11" s="21" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="21" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="21" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="B14" s="20" t="s">
+      <c r="B14" s="21" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="B15" s="20" t="s">
+      <c r="B15" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="17" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="18" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="17" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="18" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="17" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="18" t="s">
         <v>65</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
         <v>66</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="17" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="18" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="18" t="s">
         <v>68</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="19" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
         <v>70</v>
       </c>
-      <c r="B26" s="20" t="s">
+      <c r="B26" s="21" t="s">
         <v>71</v>
       </c>
-      <c r="C26" s="20" t="s">
+      <c r="C26" s="21" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
         <v>73</v>
       </c>
-      <c r="B27" s="20" t="s">
+      <c r="B27" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="C27" s="20" t="s">
+      <c r="C27" s="21" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="19" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="23" t="s">
+      <c r="A30" s="24" t="s">
         <v>77</v>
       </c>
-      <c r="B30" s="23" t="s">
+      <c r="B30" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="C30" s="23" t="s">
+      <c r="C30" s="24" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="B31" s="22" t="s">
+      <c r="B31" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="21" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="B32" s="22" t="s">
+      <c r="B32" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C32" s="20" t="s">
+      <c r="C32" s="21" t="s">
         <v>83</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="23" t="s">
         <v>53</v>
       </c>
-      <c r="C33" s="20" t="s">
+      <c r="C33" s="21" t="s">
         <v>85</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
         <v>86</v>
       </c>
-      <c r="B34" s="22" t="s">
+      <c r="B34" s="23" t="s">
         <v>57</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="21" t="s">
         <v>87</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="B35" s="22" t="s">
+      <c r="B35" s="23" t="s">
         <v>55</v>
       </c>
-      <c r="C35" s="20" t="s">
+      <c r="C35" s="21" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="B36" s="22" t="s">
+      <c r="B36" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="21" t="s">
         <v>91</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="B37" s="22" t="s">
+      <c r="B37" s="23" t="s">
         <v>59</v>
       </c>
-      <c r="C37" s="20" t="s">
+      <c r="C37" s="21" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="s">
         <v>94</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
         <v>96</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
         <v>97</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="19" t="s">
         <v>98</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
         <v>99</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="18" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="19" t="s">
         <v>100</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="17" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="18" t="s">
         <v>101</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="17" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="18" t="s">
         <v>102</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="17" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="18" t="s">
         <v>103</v>
       </c>
     </row>
@@ -2215,340 +2219,340 @@
   <dimension ref="A1:D44"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>104</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>105</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="25" t="n">
         <v>850000</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="25" t="n">
         <v>480000</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <f aca="false">B5+B6</f>
         <v>1330000</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="25" t="n">
         <v>9000000</v>
       </c>
-      <c r="D10" s="20" t="s">
+      <c r="D10" s="21" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="27" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="28" t="n">
         <f aca="false">B10/(1+B11)</f>
         <v>7200000</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="27" t="n">
         <v>0.45</v>
       </c>
-      <c r="D13" s="20" t="s">
+      <c r="D13" s="21" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <f aca="false">B12*(1-B13)</f>
         <v>3960000</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="D14" s="21" t="s">
         <v>120</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="28" t="n">
         <f aca="false">B14*(1+B11)</f>
         <v>4950000</v>
       </c>
-      <c r="D15" s="20" t="s">
+      <c r="D15" s="21" t="s">
         <v>122</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <f aca="false">B10*B16</f>
         <v>2250000</v>
       </c>
-      <c r="D17" s="20" t="s">
+      <c r="D17" s="21" t="s">
         <v>125</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="29" t="n">
         <v>360</v>
       </c>
-      <c r="D18" s="20" t="s">
+      <c r="D18" s="21" t="s">
         <v>127</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
         <v>128</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="D21" s="20" t="s">
+      <c r="D21" s="21" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B22" s="28" t="n">
         <f aca="false">B14*B21/B18</f>
         <v>220000</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="D23" s="20" t="s">
+      <c r="D23" s="21" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="27" t="n">
+      <c r="B24" s="28" t="n">
         <f aca="false">B17*B23/B18</f>
         <v>125000</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="25" t="n">
         <v>200000</v>
       </c>
-      <c r="D25" s="20" t="s">
+      <c r="D25" s="21" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B26" s="26" t="n">
         <f aca="false">B22+B24+B25</f>
         <v>545000</v>
       </c>
-      <c r="D26" s="20" t="s">
+      <c r="D26" s="21" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="28" t="n">
         <f aca="false">B7</f>
         <v>1330000</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="B30" s="27" t="n">
+      <c r="B30" s="28" t="n">
         <f aca="false">B26</f>
         <v>545000</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="22" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B31" s="25" t="n">
+      <c r="B31" s="26" t="n">
         <f aca="false">B29+B30</f>
         <v>1875000</v>
       </c>
-      <c r="D31" s="20" t="s">
+      <c r="D31" s="21" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="B32" s="29" t="n">
+      <c r="B32" s="30" t="n">
         <f aca="false">B30/B31</f>
         <v>0.290666666666667</v>
       </c>
-      <c r="D32" s="20" t="s">
+      <c r="D32" s="21" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="18" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="B35" s="30" t="str">
+      <c r="B35" s="31" t="str">
         <f aca="false">IF(ABS(B7+B22+B24+B25-B31)&lt;1,"OK — anleggsmidler, varelager, kundefordringer og reserve summerer seg til kapitalbehovet","AVVIK: postene summerer seg ikke til kapitalbehovet")</f>
         <v>OK — anleggsmidler, varelager, kundefordringer og reserve summerer seg til kapitalbehovet</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="B36" s="30" t="str">
+      <c r="B36" s="31" t="str">
         <f aca="false">IF(ABS(B12*(1+B11)-B10)&lt;1,"OK — salgsinntekten uten mva. ganget opp med satsen gir salget inkl. mva.","AVVIK: mva.-omregningen stemmer ikke")</f>
         <v>OK — salgsinntekten uten mva. ganget opp med satsen gir salget inkl. mva.</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="B37" s="30" t="str">
+      <c r="B37" s="31" t="str">
         <f aca="false">IF(AND(B13&gt;0,B13&lt;1,B16&gt;=0,B16&lt;=1,B21&gt;=0,B23&gt;=0,B18&gt;0),"OK — bruttofortjeneste og kredittandel ligger mellom null og hundre prosent, og dagene er ikke negative","AVVIK: en av forutsetningene er umulig — sjekk prosentene og dagene")</f>
         <v>OK — bruttofortjeneste og kredittandel ligger mellom null og hundre prosent, og dagene er ikke negative</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="18" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="19" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="20" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="B40" s="27" t="n">
+      <c r="B40" s="28" t="n">
         <f aca="false">B17/B18</f>
         <v>6250</v>
       </c>
-      <c r="D40" s="20" t="s">
+      <c r="D40" s="21" t="s">
         <v>152</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="B41" s="27" t="n">
+      <c r="B41" s="28" t="n">
         <f aca="false">B14/B18</f>
         <v>11000</v>
       </c>
-      <c r="D41" s="20" t="s">
+      <c r="D41" s="21" t="s">
         <v>154</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="22" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="23" t="s">
         <v>155</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="17" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="18" t="s">
         <v>156</v>
       </c>
     </row>
@@ -2586,341 +2590,341 @@
   <dimension ref="A1:F31"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="0" width="20"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="50"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="2" style="1" width="20"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="50"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>157</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>158</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B5" s="27" t="n">
+      <c r="B5" s="28" t="n">
         <f aca="false">Kapitalbehov!B17</f>
         <v>2250000</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B6" s="31" t="n">
+      <c r="B6" s="32" t="n">
         <f aca="false">Kapitalbehov!B18</f>
         <v>360</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="B7" s="27" t="n">
+      <c r="B7" s="28" t="n">
         <f aca="false">Kapitalbehov!B31-Kapitalbehov!B24</f>
         <v>1750000</v>
       </c>
-      <c r="F7" s="20" t="s">
+      <c r="F7" s="21" t="s">
         <v>161</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="20" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="21" t="s">
         <v>162</v>
       </c>
-      <c r="B8" s="32" t="n">
+      <c r="B8" s="33" t="n">
         <f aca="false">Kapitalbehov!B23</f>
         <v>20</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="29" t="n">
+      <c r="B9" s="30" t="n">
         <f aca="false">Finansiering!B5</f>
         <v>0.3</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="B11" s="23" t="s">
+      <c r="B11" s="24" t="s">
         <v>134</v>
       </c>
-      <c r="C11" s="23" t="s">
+      <c r="C11" s="24" t="s">
         <v>53</v>
       </c>
-      <c r="D11" s="23" t="s">
+      <c r="D11" s="24" t="s">
         <v>165</v>
       </c>
-      <c r="E11" s="23" t="s">
+      <c r="E11" s="24" t="s">
         <v>166</v>
       </c>
-      <c r="F11" s="23" t="s">
+      <c r="F11" s="24" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="28" t="n">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="29" t="n">
         <v>0</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="28" t="n">
         <f aca="false">$B$5*A12/$B$6</f>
         <v>0</v>
       </c>
-      <c r="C12" s="27" t="n">
+      <c r="C12" s="28" t="n">
         <f aca="false">$B$7+B12</f>
         <v>1750000</v>
       </c>
-      <c r="D12" s="27" t="n">
+      <c r="D12" s="28" t="n">
         <f aca="false">C12-($B$7+$B$5*$B$8/$B$6)</f>
         <v>-125000</v>
       </c>
-      <c r="E12" s="27" t="n">
+      <c r="E12" s="28" t="n">
         <f aca="false">C12*$B$9</f>
         <v>525000</v>
       </c>
-      <c r="F12" s="20" t="s">
+      <c r="F12" s="21" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="n">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="29" t="n">
         <v>10</v>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="28" t="n">
         <f aca="false">$B$5*A13/$B$6</f>
         <v>62500</v>
       </c>
-      <c r="C13" s="27" t="n">
+      <c r="C13" s="28" t="n">
         <f aca="false">$B$7+B13</f>
         <v>1812500</v>
       </c>
-      <c r="D13" s="27" t="n">
+      <c r="D13" s="28" t="n">
         <f aca="false">C13-($B$7+$B$5*$B$8/$B$6)</f>
         <v>-62500</v>
       </c>
-      <c r="E13" s="27" t="n">
+      <c r="E13" s="28" t="n">
         <f aca="false">C13*$B$9</f>
         <v>543750</v>
       </c>
-      <c r="F13" s="20" t="s">
+      <c r="F13" s="21" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="28" t="n">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="29" t="n">
         <v>20</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="28" t="n">
         <f aca="false">$B$5*A14/$B$6</f>
         <v>125000</v>
       </c>
-      <c r="C14" s="27" t="n">
+      <c r="C14" s="28" t="n">
         <f aca="false">$B$7+B14</f>
         <v>1875000</v>
       </c>
-      <c r="D14" s="27" t="n">
+      <c r="D14" s="28" t="n">
         <f aca="false">C14-($B$7+$B$5*$B$8/$B$6)</f>
         <v>0</v>
       </c>
-      <c r="E14" s="27" t="n">
+      <c r="E14" s="28" t="n">
         <f aca="false">C14*$B$9</f>
         <v>562500</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="F14" s="21" t="s">
         <v>170</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="31" t="n">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="32" t="n">
         <f aca="false">$B$8</f>
         <v>20</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <f aca="false">$B$5*A15/$B$6</f>
         <v>125000</v>
       </c>
-      <c r="C15" s="25" t="n">
+      <c r="C15" s="26" t="n">
         <f aca="false">$B$7+B15</f>
         <v>1875000</v>
       </c>
-      <c r="D15" s="27" t="n">
+      <c r="D15" s="28" t="n">
         <f aca="false">C15-($B$7+$B$5*$B$8/$B$6)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="27" t="n">
+      <c r="E15" s="28" t="n">
         <f aca="false">C15*$B$9</f>
         <v>562500</v>
       </c>
-      <c r="F15" s="20" t="s">
+      <c r="F15" s="21" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="28" t="n">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="28" t="n">
         <f aca="false">$B$5*A16/$B$6</f>
         <v>187500</v>
       </c>
-      <c r="C16" s="27" t="n">
+      <c r="C16" s="28" t="n">
         <f aca="false">$B$7+B16</f>
         <v>1937500</v>
       </c>
-      <c r="D16" s="27" t="n">
+      <c r="D16" s="28" t="n">
         <f aca="false">C16-($B$7+$B$5*$B$8/$B$6)</f>
         <v>62500</v>
       </c>
-      <c r="E16" s="27" t="n">
+      <c r="E16" s="28" t="n">
         <f aca="false">C16*$B$9</f>
         <v>581250</v>
       </c>
-      <c r="F16" s="20" t="s">
+      <c r="F16" s="21" t="s">
         <v>172</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="n">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <f aca="false">$B$5*A17/$B$6</f>
         <v>250000</v>
       </c>
-      <c r="C17" s="27" t="n">
+      <c r="C17" s="28" t="n">
         <f aca="false">$B$7+B17</f>
         <v>2000000</v>
       </c>
-      <c r="D17" s="27" t="n">
+      <c r="D17" s="28" t="n">
         <f aca="false">C17-($B$7+$B$5*$B$8/$B$6)</f>
         <v>125000</v>
       </c>
-      <c r="E17" s="27" t="n">
+      <c r="E17" s="28" t="n">
         <f aca="false">C17*$B$9</f>
         <v>600000</v>
       </c>
-      <c r="F17" s="20" t="s">
+      <c r="F17" s="21" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="28" t="n">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="29" t="n">
         <v>60</v>
       </c>
-      <c r="B18" s="27" t="n">
+      <c r="B18" s="28" t="n">
         <f aca="false">$B$5*A18/$B$6</f>
         <v>375000</v>
       </c>
-      <c r="C18" s="27" t="n">
+      <c r="C18" s="28" t="n">
         <f aca="false">$B$7+B18</f>
         <v>2125000</v>
       </c>
-      <c r="D18" s="27" t="n">
+      <c r="D18" s="28" t="n">
         <f aca="false">C18-($B$7+$B$5*$B$8/$B$6)</f>
         <v>250000</v>
       </c>
-      <c r="E18" s="27" t="n">
+      <c r="E18" s="28" t="n">
         <f aca="false">C18*$B$9</f>
         <v>637500</v>
       </c>
-      <c r="F18" s="20" t="s">
+      <c r="F18" s="21" t="s">
         <v>174</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="n">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="29" t="n">
         <v>90</v>
       </c>
-      <c r="B19" s="27" t="n">
+      <c r="B19" s="28" t="n">
         <f aca="false">$B$5*A19/$B$6</f>
         <v>562500</v>
       </c>
-      <c r="C19" s="27" t="n">
+      <c r="C19" s="28" t="n">
         <f aca="false">$B$7+B19</f>
         <v>2312500</v>
       </c>
-      <c r="D19" s="27" t="n">
+      <c r="D19" s="28" t="n">
         <f aca="false">C19-($B$7+$B$5*$B$8/$B$6)</f>
         <v>437500</v>
       </c>
-      <c r="E19" s="27" t="n">
+      <c r="E19" s="28" t="n">
         <f aca="false">C19*$B$9</f>
         <v>693750</v>
       </c>
-      <c r="F19" s="20" t="s">
+      <c r="F19" s="21" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="18" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="19" t="s">
         <v>176</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="22" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="23" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
         <v>179</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="C27" s="30" t="str">
+      <c r="C27" s="31" t="str">
         <f aca="false">IF(ABS(C15-Kapitalbehov!B31)&lt;1,"OK — raden gir samme kapitalbehov som arket Kapitalbehov","AVVIK: raden stemmer ikke med kalkulatoren")</f>
         <v>OK — raden gir samme kapitalbehov som arket Kapitalbehov</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="C28" s="30" t="str">
+      <c r="C28" s="31" t="str">
         <f aca="false">IF(AND(C12&lt;C13,C15&lt;C16,C17&lt;C18),"OK — lengre kredittid binder mer kapital, hele tabellen igjennom","AVVIK: tabellen skal stige nedover")</f>
         <v>OK — lengre kredittid binder mer kapital, hele tabellen igjennom</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="C29" s="30" t="str">
+      <c r="C29" s="31" t="str">
         <f aca="false">IF(B12=0,"OK — uten kreditt er ingen kapital bundet hos kundene","AVVIK: null dagers kredittid skal gi null i kundefordringer")</f>
         <v>OK — uten kreditt er ingen kapital bundet hos kundene</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="17" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="18" t="s">
         <v>183</v>
       </c>
     </row>
@@ -2958,365 +2962,365 @@
   <dimension ref="A1:E42"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="42"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="34"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="52"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="42"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="52"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>184</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>185</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>186</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B5" s="26" t="n">
+      <c r="B5" s="27" t="n">
         <v>0.3</v>
       </c>
-      <c r="E5" s="20" t="s">
+      <c r="E5" s="21" t="s">
         <v>188</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>189</v>
       </c>
-      <c r="B6" s="26" t="n">
+      <c r="B6" s="27" t="n">
         <v>0.5</v>
       </c>
-      <c r="E6" s="20" t="s">
+      <c r="E6" s="21" t="s">
         <v>190</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="20" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="21" t="s">
         <v>191</v>
       </c>
-      <c r="B7" s="28" t="n">
+      <c r="B7" s="29" t="n">
         <v>15</v>
       </c>
-      <c r="E7" s="20" t="s">
+      <c r="E7" s="21" t="s">
         <v>192</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
         <v>193</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
         <v>194</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <f aca="false">Kapitalbehov!B31</f>
         <v>1875000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="B11" s="25" t="n">
+      <c r="B11" s="26" t="n">
         <f aca="false">B10*B5</f>
         <v>562500</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="28" t="n">
         <f aca="false">Kapitalbehov!B7+Kapitalbehov!B22*B6</f>
         <v>1440000</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>197</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="22" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="23" t="s">
         <v>198</v>
       </c>
-      <c r="B13" s="25" t="n">
+      <c r="B13" s="26" t="n">
         <f aca="false">B12-B11</f>
         <v>877500</v>
       </c>
-      <c r="E13" s="20" t="s">
+      <c r="E13" s="21" t="s">
         <v>199</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="21" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="27" t="n">
+      <c r="B14" s="28" t="n">
         <f aca="false">B10-B11</f>
         <v>1312500</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="22" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="23" t="s">
         <v>201</v>
       </c>
-      <c r="B15" s="25" t="n">
+      <c r="B15" s="26" t="n">
         <f aca="false">B14-B13</f>
         <v>435000</v>
       </c>
-      <c r="E15" s="20" t="s">
+      <c r="E15" s="21" t="s">
         <v>202</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
         <v>203</v>
       </c>
-      <c r="B16" s="27" t="n">
+      <c r="B16" s="28" t="n">
         <f aca="false">Kapitalbehov!B15*B7/Kapitalbehov!B18</f>
         <v>206250</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
         <v>204</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <f aca="false">B15-B16</f>
         <v>228750</v>
       </c>
-      <c r="E17" s="20" t="s">
+      <c r="E17" s="21" t="s">
         <v>205</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
         <v>206</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="20" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B20" s="24" t="n">
+      <c r="B20" s="25" t="n">
         <v>400000</v>
       </c>
-      <c r="E20" s="20" t="s">
+      <c r="E20" s="21" t="s">
         <v>208</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B21" s="33" t="n">
+      <c r="B21" s="34" t="n">
         <f aca="false">B20/B10</f>
         <v>0.213333333333333</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
         <v>210</v>
       </c>
-      <c r="B22" s="25" t="n">
+      <c r="B22" s="26" t="n">
         <f aca="false">B11-B20</f>
         <v>162500</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>211</v>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="28" t="n">
         <f aca="false">B20/B5</f>
         <v>1333333.33333333</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="21" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="E24" s="34" t="str">
+      <c r="E24" s="35" t="str">
         <f aca="false">IF(B21&gt;=B5,"Kravet er innfridd","Kravet er ikke innfridd — kapitalbehovet må ned eller egenkapitalen opp")</f>
         <v>Kravet er ikke innfridd — kapitalbehovet må ned eller egenkapitalen opp</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="19" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="23" t="s">
+      <c r="A27" s="24" t="s">
         <v>215</v>
       </c>
-      <c r="B27" s="23" t="s">
+      <c r="B27" s="24" t="s">
         <v>216</v>
       </c>
-      <c r="C27" s="23" t="s">
+      <c r="C27" s="24" t="s">
         <v>217</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="24" t="s">
         <v>216</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="20" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B28" s="27" t="n">
+      <c r="B28" s="28" t="n">
         <f aca="false">Kapitalbehov!B5</f>
         <v>850000</v>
       </c>
-      <c r="C28" s="20" t="s">
+      <c r="C28" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="D28" s="27" t="n">
+      <c r="D28" s="28" t="n">
         <f aca="false">B11</f>
         <v>562500</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="28" t="n">
         <f aca="false">Kapitalbehov!B6</f>
         <v>480000</v>
       </c>
-      <c r="C29" s="20" t="s">
+      <c r="C29" s="21" t="s">
         <v>218</v>
       </c>
-      <c r="D29" s="27" t="n">
+      <c r="D29" s="28" t="n">
         <f aca="false">B13</f>
         <v>877500</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B30" s="27" t="n">
+      <c r="B30" s="28" t="n">
         <f aca="false">Kapitalbehov!B22</f>
         <v>220000</v>
       </c>
-      <c r="C30" s="20" t="s">
+      <c r="C30" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="D30" s="27" t="n">
+      <c r="D30" s="28" t="n">
         <f aca="false">B16</f>
         <v>206250</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="28" t="n">
         <f aca="false">Kapitalbehov!B24</f>
         <v>125000</v>
       </c>
-      <c r="C31" s="20" t="s">
+      <c r="C31" s="21" t="s">
         <v>220</v>
       </c>
-      <c r="D31" s="27" t="n">
+      <c r="D31" s="28" t="n">
         <f aca="false">B17</f>
         <v>228750</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="B32" s="27" t="n">
+      <c r="B32" s="28" t="n">
         <f aca="false">Kapitalbehov!B25</f>
         <v>200000</v>
       </c>
-      <c r="C32" s="20"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="22" t="s">
+      <c r="C32" s="21"/>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="23" t="s">
         <v>222</v>
       </c>
-      <c r="B33" s="25" t="n">
+      <c r="B33" s="26" t="n">
         <f aca="false">SUM(B28:B32)</f>
         <v>1875000</v>
       </c>
-      <c r="C33" s="22" t="s">
+      <c r="C33" s="23" t="s">
         <v>223</v>
       </c>
-      <c r="D33" s="25" t="n">
+      <c r="D33" s="26" t="n">
         <f aca="false">SUM(D28:D32)</f>
         <v>1875000</v>
       </c>
-      <c r="E33" s="20" t="s">
+      <c r="E33" s="21" t="s">
         <v>224</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
         <v>225</v>
       </c>
-      <c r="B36" s="30" t="str">
+      <c r="B36" s="31" t="str">
         <f aca="false">IF(ABS(B33-D33)&lt;1,"OK — eiendeler er lik egenkapital og gjeld","AVVIK: åpningsbalansen balanserer ikke")</f>
         <v>OK — eiendeler er lik egenkapital og gjeld</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="20" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="21" t="s">
         <v>226</v>
       </c>
-      <c r="B37" s="30" t="str">
+      <c r="B37" s="31" t="str">
         <f aca="false">IF(ABS(B11+B13+B15-B10)&lt;1,"OK — egenkapital, langsiktig og kortsiktig gjeld dekker kapitalbehovet","AVVIK: finansieringsplanen summerer seg ikke til kapitalbehovet")</f>
         <v>OK — egenkapital, langsiktig og kortsiktig gjeld dekker kapitalbehovet</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
         <v>227</v>
       </c>
-      <c r="B38" s="30" t="str">
+      <c r="B38" s="31" t="str">
         <f aca="false">IF(B11+B13&gt;=B12-1,"OK — langsiktig kapital dekker anleggsmidlene og den varige delen av lageret","AVVIK: anleggsmidlene er delvis finansiert med kortsiktig gjeld — det er slik bedrifter går tomme for penger")</f>
         <v>OK — langsiktig kapital dekker anleggsmidlene og den varige delen av lageret</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
         <v>228</v>
       </c>
-      <c r="B39" s="30" t="str">
+      <c r="B39" s="31" t="str">
         <f aca="false">IF(B17&gt;=0,"OK — leverandørkreditten får plass innenfor den kortsiktige gjelda","AVVIK: leverandørkreditten alene overstiger det kortsiktige lånebehovet — da må mer finansieres langsiktig")</f>
         <v>OK — leverandørkreditten får plass innenfor den kortsiktige gjelda</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="22" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="23" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
         <v>230</v>
       </c>
     </row>
@@ -3359,709 +3363,709 @@
   <dimension ref="A1:E87"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="46"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="0" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="54"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="46"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="2" style="1" width="18"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="54"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>231</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>233</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="17" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="18" t="s">
         <v>234</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23" t="s">
+      <c r="A7" s="24"/>
+      <c r="B7" s="24" t="s">
         <v>235</v>
       </c>
-      <c r="C7" s="23" t="s">
+      <c r="C7" s="24" t="s">
         <v>236</v>
       </c>
-      <c r="D7" s="23"/>
-      <c r="E7" s="23" t="s">
+      <c r="D7" s="24"/>
+      <c r="E7" s="24" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="22" t="s">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A8" s="23" t="s">
         <v>164</v>
       </c>
-      <c r="B8" s="35" t="n">
+      <c r="B8" s="36" t="n">
         <f aca="false">Kapitalbehov!B23</f>
         <v>20</v>
       </c>
-      <c r="C8" s="28" t="n">
+      <c r="C8" s="29" t="n">
         <v>40</v>
       </c>
-      <c r="E8" s="20" t="s">
+      <c r="E8" s="21" t="s">
         <v>237</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="20" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B9" s="27" t="n">
+      <c r="B9" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$17*B8/Kapitalbehov!$B$18</f>
         <v>125000</v>
       </c>
-      <c r="C9" s="27" t="n">
+      <c r="C9" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$17*C8/Kapitalbehov!$B$18</f>
         <v>250000</v>
       </c>
-      <c r="E9" s="20" t="s">
+      <c r="E9" s="21" t="s">
         <v>238</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="22" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="B10" s="25" t="n">
+      <c r="B10" s="26" t="n">
         <f aca="false">Kapitalbehov!$B$31-Kapitalbehov!$B$24+B9</f>
         <v>1875000</v>
       </c>
-      <c r="C10" s="25" t="n">
+      <c r="C10" s="26" t="n">
         <f aca="false">Kapitalbehov!$B$31-Kapitalbehov!$B$24+C9</f>
         <v>2000000</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
         <v>166</v>
       </c>
-      <c r="B11" s="27" t="n">
+      <c r="B11" s="28" t="n">
         <f aca="false">B10*Finansiering!$B$5</f>
         <v>562500</v>
       </c>
-      <c r="C11" s="27" t="n">
+      <c r="C11" s="28" t="n">
         <f aca="false">C10*Finansiering!$B$5</f>
         <v>600000</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="22" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="23" t="s">
         <v>240</v>
       </c>
-      <c r="C12" s="25" t="n">
+      <c r="C12" s="26" t="n">
         <f aca="false">C11-B11</f>
         <v>37500</v>
       </c>
-      <c r="E12" s="20" t="s">
+      <c r="E12" s="21" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
         <v>242</v>
       </c>
-      <c r="B13" s="27" t="n">
+      <c r="B13" s="28" t="n">
         <f aca="false">Kapitalbehov!B40</f>
         <v>6250</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="18" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
         <v>243</v>
       </c>
-      <c r="B16" s="30" t="str">
+      <c r="B16" s="31" t="str">
         <f aca="false">IF(AND(C8&gt;B8,C10&gt;B10),"OK — lengre kredittid binder mer kapital og krever mer egenkapital","AVVIK: sett en lengre kredittid i C8 enn den i B8")</f>
         <v>OK — lengre kredittid binder mer kapital og krever mer egenkapital</v>
       </c>
     </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="18" t="s">
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="19" t="s">
         <v>244</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="17" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="18" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="27.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="23"/>
-      <c r="B22" s="23" t="s">
+      <c r="A22" s="24"/>
+      <c r="B22" s="24" t="s">
         <v>246</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="24" t="s">
         <v>247</v>
       </c>
-      <c r="D22" s="23" t="s">
+      <c r="D22" s="24" t="s">
         <v>248</v>
       </c>
-      <c r="E22" s="23" t="s">
+      <c r="E22" s="24" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>249</v>
       </c>
-      <c r="B23" s="27" t="n">
+      <c r="B23" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$7</f>
         <v>1330000</v>
       </c>
-      <c r="C23" s="27" t="n">
+      <c r="C23" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$5</f>
         <v>850000</v>
       </c>
-      <c r="D23" s="27" t="n">
+      <c r="D23" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$5</f>
         <v>850000</v>
       </c>
-      <c r="E23" s="20" t="s">
+      <c r="E23" s="21" t="s">
         <v>250</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="22" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="B24" s="31" t="n">
+      <c r="B24" s="32" t="n">
         <f aca="false">Kapitalbehov!$B$21</f>
         <v>20</v>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="32" t="n">
         <f aca="false">Kapitalbehov!$B$21</f>
         <v>20</v>
       </c>
-      <c r="D24" s="28" t="n">
+      <c r="D24" s="29" t="n">
         <v>14</v>
       </c>
-      <c r="E24" s="20" t="s">
+      <c r="E24" s="21" t="s">
         <v>251</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B25" s="27" t="n">
+      <c r="B25" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$14*B24/Kapitalbehov!$B$18</f>
         <v>220000</v>
       </c>
-      <c r="C25" s="27" t="n">
+      <c r="C25" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$14*C24/Kapitalbehov!$B$18</f>
         <v>220000</v>
       </c>
-      <c r="D25" s="27" t="n">
+      <c r="D25" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$14*D24/Kapitalbehov!$B$18</f>
         <v>154000</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="20" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B26" s="27" t="n">
+      <c r="B26" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$24</f>
         <v>125000</v>
       </c>
-      <c r="C26" s="27" t="n">
+      <c r="C26" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$24</f>
         <v>125000</v>
       </c>
-      <c r="D26" s="27" t="n">
+      <c r="D26" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$24</f>
         <v>125000</v>
       </c>
     </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="20" t="s">
+    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B27" s="27" t="n">
+      <c r="B27" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$25</f>
         <v>200000</v>
       </c>
-      <c r="C27" s="27" t="n">
+      <c r="C27" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$25</f>
         <v>200000</v>
       </c>
-      <c r="D27" s="27" t="n">
+      <c r="D27" s="28" t="n">
         <f aca="false">Kapitalbehov!$B$25</f>
         <v>200000</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="22" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="23" t="s">
         <v>239</v>
       </c>
-      <c r="B28" s="25" t="n">
+      <c r="B28" s="26" t="n">
         <f aca="false">B23+B25+B26+B27</f>
         <v>1875000</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="26" t="n">
         <f aca="false">C23+C25+C26+C27</f>
         <v>1395000</v>
       </c>
-      <c r="D28" s="25" t="n">
+      <c r="D28" s="26" t="n">
         <f aca="false">D23+D25+D26+D27</f>
         <v>1329000</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="20" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="21" t="s">
         <v>207</v>
       </c>
-      <c r="B29" s="27" t="n">
+      <c r="B29" s="28" t="n">
         <f aca="false">Finansiering!$B$20</f>
         <v>400000</v>
       </c>
-      <c r="C29" s="27" t="n">
+      <c r="C29" s="28" t="n">
         <f aca="false">Finansiering!$B$20</f>
         <v>400000</v>
       </c>
-      <c r="D29" s="27" t="n">
+      <c r="D29" s="28" t="n">
         <f aca="false">Finansiering!$B$20</f>
         <v>400000</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="22" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="23" t="s">
         <v>252</v>
       </c>
-      <c r="B30" s="33" t="n">
+      <c r="B30" s="34" t="n">
         <f aca="false">B29/B28</f>
         <v>0.213333333333333</v>
       </c>
-      <c r="C30" s="33" t="n">
+      <c r="C30" s="34" t="n">
         <f aca="false">C29/C28</f>
         <v>0.28673835125448</v>
       </c>
-      <c r="D30" s="33" t="n">
+      <c r="D30" s="34" t="n">
         <f aca="false">D29/D28</f>
         <v>0.300978179082017</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
         <v>253</v>
       </c>
-      <c r="B31" s="29" t="n">
+      <c r="B31" s="30" t="n">
         <f aca="false">Finansiering!$B$5</f>
         <v>0.3</v>
       </c>
-      <c r="C31" s="29" t="n">
+      <c r="C31" s="30" t="n">
         <f aca="false">Finansiering!$B$5</f>
         <v>0.3</v>
       </c>
-      <c r="D31" s="29" t="n">
+      <c r="D31" s="30" t="n">
         <f aca="false">Finansiering!$B$5</f>
         <v>0.3</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
         <v>254</v>
       </c>
-      <c r="B32" s="27" t="n">
+      <c r="B32" s="28" t="n">
         <f aca="false">B28*B31-B29</f>
         <v>162500</v>
       </c>
-      <c r="C32" s="27" t="n">
+      <c r="C32" s="28" t="n">
         <f aca="false">C28*C31-C29</f>
         <v>18500</v>
       </c>
-      <c r="D32" s="27" t="n">
+      <c r="D32" s="28" t="n">
         <f aca="false">D28*D31-D29</f>
         <v>-1300</v>
       </c>
-      <c r="E32" s="20" t="s">
+      <c r="E32" s="21" t="s">
         <v>255</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
         <v>213</v>
       </c>
-      <c r="B33" s="34" t="str">
+      <c r="B33" s="35" t="str">
         <f aca="false">IF(B30&gt;=B31,"Over kravet","Under kravet")</f>
         <v>Under kravet</v>
       </c>
-      <c r="C33" s="34" t="str">
+      <c r="C33" s="35" t="str">
         <f aca="false">IF(C30&gt;=C31,"Over kravet","Under kravet")</f>
         <v>Under kravet</v>
       </c>
-      <c r="D33" s="34" t="str">
+      <c r="D33" s="35" t="str">
         <f aca="false">IF(D30&gt;=D31,"Over kravet","Under kravet")</f>
         <v>Over kravet</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="18" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
         <v>256</v>
       </c>
-      <c r="B36" s="30" t="str">
+      <c r="B36" s="31" t="str">
         <f aca="false">IF(C30&lt;C31,"OK — leasing løfter egenkapitalandelen, men ikke helt opp til kravet. Én knapp alene holder ikke","AVVIK: leasing alene skal ikke være nok — da mister klasseoppgaven poenget")</f>
         <v>OK — leasing løfter egenkapitalandelen, men ikke helt opp til kravet. Én knapp alene holder ikke</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="17" t="s">
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="18" t="s">
         <v>257</v>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="20" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="21" t="s">
         <v>258</v>
       </c>
-      <c r="B38" s="30" t="str">
+      <c r="B38" s="31" t="str">
         <f aca="false">IF(D30&gt;=D31,"OK — de to grepene sammen løfter dere over bankens krav","AVVIK: sett lagringstida i D24 lavere — dere er fortsatt under kravet")</f>
         <v>OK — de to grepene sammen løfter dere over bankens krav</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="18" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="19" t="s">
         <v>259</v>
       </c>
     </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="17" t="s">
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="18" t="s">
         <v>260</v>
       </c>
     </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="18" t="s">
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="19" t="s">
         <v>261</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="20" t="s">
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="21" t="s">
         <v>262</v>
       </c>
-      <c r="B45" s="24" t="n">
+      <c r="B45" s="25" t="n">
         <v>28000000</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="20" t="s">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="21" t="s">
         <v>263</v>
       </c>
-      <c r="B46" s="24" t="n">
+      <c r="B46" s="25" t="n">
         <v>8390000</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="20" t="s">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B47" s="24" t="n">
+      <c r="B47" s="25" t="n">
         <v>4200000</v>
       </c>
     </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="20" t="s">
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B48" s="24" t="n">
+      <c r="B48" s="25" t="n">
         <v>1400000</v>
       </c>
     </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="20" t="s">
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="21" t="s">
         <v>219</v>
       </c>
-      <c r="B49" s="24" t="n">
+      <c r="B49" s="25" t="n">
         <v>2100000</v>
       </c>
     </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="20" t="s">
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="21" t="s">
         <v>264</v>
       </c>
-      <c r="B50" s="24" t="n">
-        <v>1000000</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="20" t="s">
+      <c r="B50" s="25" t="n">
+        <v>982650</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="21" t="s">
         <v>265</v>
       </c>
-      <c r="B51" s="24" t="n">
+      <c r="B51" s="25" t="n">
         <v>300000</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="20" t="s">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="21" t="s">
         <v>266</v>
       </c>
-      <c r="B52" s="24" t="n">
+      <c r="B52" s="25" t="n">
         <v>1500000</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="20" t="s">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="21" t="s">
         <v>267</v>
       </c>
-      <c r="B53" s="27" t="n">
+      <c r="B53" s="28" t="n">
         <f aca="false">B52-B51</f>
         <v>1200000</v>
       </c>
-      <c r="E53" s="20" t="s">
+      <c r="E53" s="21" t="s">
         <v>268</v>
       </c>
     </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="18" t="s">
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="19" t="s">
         <v>269</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="20" t="s">
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="21" t="s">
         <v>270</v>
       </c>
-      <c r="B56" s="36" t="n">
+      <c r="B56" s="37" t="n">
         <f aca="false">B47*Kapitalbehov!B18/B45</f>
         <v>54</v>
       </c>
-      <c r="E56" s="20" t="s">
+      <c r="E56" s="21" t="s">
         <v>271</v>
       </c>
     </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="20" t="s">
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="21" t="s">
         <v>272</v>
       </c>
-      <c r="B57" s="37" t="n">
+      <c r="B57" s="38" t="n">
         <f aca="false">B48*Kapitalbehov!B18/B46</f>
         <v>60.0715137067938</v>
       </c>
     </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="20" t="s">
+    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="21" t="s">
         <v>273</v>
       </c>
-      <c r="B58" s="37" t="n">
+      <c r="B58" s="38" t="n">
         <f aca="false">B49*Kapitalbehov!B18/(B46*(1+Kapitalbehov!B11))</f>
         <v>72.0858164481526</v>
       </c>
     </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A59" s="22" t="s">
+    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="23" t="s">
         <v>274</v>
       </c>
-      <c r="B59" s="25" t="n">
+      <c r="B59" s="26" t="n">
         <f aca="false">B48+B47-B49</f>
         <v>3500000</v>
       </c>
-      <c r="E59" s="20" t="s">
+      <c r="E59" s="21" t="s">
         <v>275</v>
       </c>
     </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A60" s="20" t="s">
+    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="21" t="s">
         <v>276</v>
       </c>
-      <c r="B60" s="27" t="n">
+      <c r="B60" s="28" t="n">
         <f aca="false">B45/Kapitalbehov!B18</f>
         <v>77777.7777777778</v>
       </c>
     </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A62" s="18" t="s">
+    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A62" s="19" t="s">
         <v>277</v>
       </c>
     </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A63" s="20" t="s">
+    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A63" s="21" t="s">
         <v>278</v>
       </c>
-      <c r="B63" s="24" t="n">
+      <c r="B63" s="25" t="n">
         <v>1500000</v>
       </c>
     </row>
-    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="20" t="s">
+    <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A64" s="21" t="s">
         <v>279</v>
       </c>
-      <c r="B64" s="26" t="n">
+      <c r="B64" s="27" t="n">
         <v>0.08</v>
       </c>
     </row>
-    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A65" s="20" t="s">
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="21" t="s">
         <v>280</v>
       </c>
-      <c r="B65" s="26" t="n">
+      <c r="B65" s="27" t="n">
         <v>0.005</v>
       </c>
     </row>
-    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A66" s="22" t="s">
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="23" t="s">
         <v>281</v>
       </c>
-      <c r="B66" s="25" t="n">
+      <c r="B66" s="26" t="n">
         <f aca="false">B63*B64+B63*B65</f>
         <v>127500</v>
       </c>
-      <c r="E66" s="20" t="s">
+      <c r="E66" s="21" t="s">
         <v>282</v>
       </c>
     </row>
-    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="18" t="s">
+    <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="19" t="s">
         <v>283</v>
       </c>
     </row>
-    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="20" t="s">
+    <row r="69" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A69" s="21" t="s">
         <v>284</v>
       </c>
-      <c r="B69" s="28" t="n">
+      <c r="B69" s="29" t="n">
         <v>30</v>
       </c>
-      <c r="E69" s="20" t="s">
+      <c r="E69" s="21" t="s">
         <v>285</v>
       </c>
     </row>
-    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="20" t="s">
+    <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A70" s="21" t="s">
         <v>286</v>
       </c>
-      <c r="B70" s="27" t="n">
+      <c r="B70" s="28" t="n">
         <f aca="false">B45*B69/Kapitalbehov!B18</f>
         <v>2333333.33333333</v>
       </c>
     </row>
-    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="22" t="s">
+    <row r="71" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A71" s="23" t="s">
         <v>287</v>
       </c>
-      <c r="B71" s="25" t="n">
+      <c r="B71" s="26" t="n">
         <f aca="false">B47-B70</f>
         <v>1866666.66666667</v>
       </c>
     </row>
-    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="20" t="s">
+    <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A72" s="21" t="s">
         <v>288</v>
       </c>
-      <c r="B72" s="27" t="n">
+      <c r="B72" s="28" t="n">
         <f aca="false">B71*B64</f>
         <v>149333.333333333</v>
       </c>
     </row>
-    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="20" t="s">
+    <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A73" s="21" t="s">
         <v>289</v>
       </c>
-      <c r="B73" s="25" t="n">
+      <c r="B73" s="26" t="n">
         <f aca="false">B71-B53</f>
         <v>666666.666666667</v>
       </c>
-      <c r="E73" s="20" t="s">
+      <c r="E73" s="21" t="s">
         <v>290</v>
       </c>
     </row>
-    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="18" t="s">
+    <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="19" t="s">
         <v>291</v>
       </c>
     </row>
-    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A76" s="20" t="s">
+    <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="21" t="s">
         <v>292</v>
       </c>
-      <c r="B76" s="24" t="n">
+      <c r="B76" s="25" t="n">
         <v>24000000</v>
       </c>
     </row>
-    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A77" s="20" t="s">
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="21" t="s">
         <v>293</v>
       </c>
-      <c r="B77" s="29" t="n">
+      <c r="B77" s="30" t="n">
         <f aca="false">B76/(B45/(1+Kapitalbehov!B11))-1</f>
         <v>0.0714285714285714</v>
       </c>
     </row>
-    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="22" t="s">
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="23" t="s">
         <v>294</v>
       </c>
-      <c r="B78" s="25" t="n">
+      <c r="B78" s="26" t="n">
         <f aca="false">B59*(1+B77)</f>
         <v>3750000</v>
       </c>
     </row>
-    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="20" t="s">
+    <row r="79" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A79" s="21" t="s">
         <v>295</v>
       </c>
-      <c r="B79" s="27" t="n">
+      <c r="B79" s="28" t="n">
         <f aca="false">B78-B59</f>
         <v>250000</v>
       </c>
-      <c r="E79" s="20" t="s">
+      <c r="E79" s="21" t="s">
         <v>296</v>
       </c>
     </row>
-    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="18" t="s">
+    <row r="81" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A81" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="20" t="s">
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A82" s="21" t="s">
         <v>297</v>
       </c>
-      <c r="B82" s="30" t="str">
+      <c r="B82" s="31" t="str">
         <f aca="false">IF(B71&gt;B53,"OK — å hente kredittiden ned til målet frigjør mer enn hele den ubenyttede kassekredittrammen. Problemet er ikke rammen","AVVIK: med dette målet frigjør kortere kredittid mindre enn den ubenyttede rammen — sett et strammere mål i B69")</f>
         <v>OK — å hente kredittiden ned til målet frigjør mer enn hele den ubenyttede kassekredittrammen. Problemet er ikke rammen</v>
       </c>
     </row>
-    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="20" t="s">
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A83" s="21" t="s">
         <v>298</v>
       </c>
-      <c r="B83" s="30" t="str">
+      <c r="B83" s="31" t="str">
         <f aca="false">IF(B56&gt;Kapitalbehov!B23,"OK — kundene bruker lengre tid enn fristen dere har avtalt. Det er der pengene ligger","AVVIK: kundene betaler innenfor fristen — da må forklaringen på tom konto ligge et annet sted")</f>
         <v>OK — kundene bruker lengre tid enn fristen dere har avtalt. Det er der pengene ligger</v>
       </c>
     </row>
-    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="20" t="s">
+    <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A84" s="21" t="s">
         <v>299</v>
       </c>
-      <c r="B84" s="30" t="str">
+      <c r="B84" s="31" t="str">
         <f aca="false">IF(B59&gt;B50+B53,"AVVIK: det som er bundet i lager og fordringer er større enn kontanter og ubenyttet ramme til sammen — kontoen går tom før året er omme","OK — det som er bundet i driften dekkes av kontanter og ubenyttet ramme")</f>
         <v>AVVIK: det som er bundet i lager og fordringer er større enn kontanter og ubenyttet ramme til sammen — kontoen går tom før året er omme</v>
       </c>
     </row>
-    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A85" s="17" t="s">
+    <row r="85" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A85" s="18" t="s">
         <v>300</v>
       </c>
     </row>
-    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A87" s="17" t="s">
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A87" s="18" t="s">
         <v>301</v>
       </c>
     </row>
@@ -4114,300 +4118,300 @@
   <dimension ref="A1:D43"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="44"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="16"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="14"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="44"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="56"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="17.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
+    <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A1" s="2" t="s">
         <v>302</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="16" t="s">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="17" t="s">
         <v>303</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="18" t="s">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="19" t="s">
         <v>304</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="20" t="s">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A5" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="B5" s="24" t="n">
+      <c r="B5" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="20" t="s">
+      <c r="D5" s="21" t="s">
         <v>305</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="20" t="s">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A6" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="B6" s="24" t="n">
+      <c r="B6" s="25" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="20" t="s">
+      <c r="D6" s="21" t="s">
         <v>306</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="22" t="s">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A7" s="23" t="s">
         <v>111</v>
       </c>
-      <c r="B7" s="25" t="n">
+      <c r="B7" s="26" t="n">
         <f aca="false">B5+B6</f>
         <v>0</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="18" t="s">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A9" s="19" t="s">
         <v>307</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="20" t="s">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A10" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="B10" s="24" t="n">
+      <c r="B10" s="25" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="B11" s="26" t="n">
+      <c r="B11" s="27" t="n">
         <v>0.25</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="20" t="s">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A12" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="B12" s="27" t="n">
+      <c r="B12" s="28" t="n">
         <f aca="false">B10/(1+B11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="20" t="s">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A13" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="B13" s="26" t="n">
+      <c r="B13" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="22" t="s">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="23" t="s">
         <v>308</v>
       </c>
-      <c r="B14" s="25" t="n">
+      <c r="B14" s="26" t="n">
         <f aca="false">B12*(1-B13)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="20" t="s">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A15" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="B15" s="27" t="n">
+      <c r="B15" s="28" t="n">
         <f aca="false">B14*(1+B11)</f>
         <v>0</v>
       </c>
     </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="20" t="s">
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A16" s="21" t="s">
         <v>309</v>
       </c>
-      <c r="B16" s="26" t="n">
+      <c r="B16" s="27" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="20" t="s">
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="B17" s="27" t="n">
+      <c r="B17" s="28" t="n">
         <f aca="false">B10*B16</f>
         <v>0</v>
       </c>
     </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="20" t="s">
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="B18" s="28" t="n">
+      <c r="B18" s="29" t="n">
         <v>360</v>
       </c>
     </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="18" t="s">
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A20" s="19" t="s">
         <v>310</v>
       </c>
     </row>
-    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="20" t="s">
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="B21" s="28" t="n">
+      <c r="B21" s="29" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="20" t="s">
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A22" s="21" t="s">
         <v>131</v>
       </c>
-      <c r="B22" s="27" t="n">
+      <c r="B22" s="28" t="n">
         <f aca="false">B14*B21/B18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="20" t="s">
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="21" t="s">
         <v>132</v>
       </c>
-      <c r="B23" s="28" t="n">
+      <c r="B23" s="29" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="20" t="s">
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="B24" s="27" t="n">
+      <c r="B24" s="28" t="n">
         <f aca="false">B17*B23/B18</f>
         <v>0</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="B25" s="24" t="n">
+      <c r="B25" s="25" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="22" t="s">
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="23" t="s">
         <v>137</v>
       </c>
-      <c r="B26" s="25" t="n">
+      <c r="B26" s="26" t="n">
         <f aca="false">B22+B24+B25</f>
         <v>0</v>
       </c>
     </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
+    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="19" t="s">
         <v>311</v>
       </c>
     </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="22" t="s">
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="23" t="s">
         <v>142</v>
       </c>
-      <c r="B29" s="25" t="n">
+      <c r="B29" s="26" t="n">
         <f aca="false">B7+B26</f>
         <v>0</v>
       </c>
     </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="21" t="s">
         <v>187</v>
       </c>
-      <c r="B30" s="26" t="n">
+      <c r="B30" s="27" t="n">
         <v>0.3</v>
       </c>
     </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A31" s="20" t="s">
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="21" t="s">
         <v>195</v>
       </c>
-      <c r="B31" s="27" t="n">
+      <c r="B31" s="28" t="n">
         <f aca="false">B29*B30</f>
         <v>0</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="20" t="s">
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="21" t="s">
         <v>196</v>
       </c>
-      <c r="B32" s="27" t="n">
+      <c r="B32" s="28" t="n">
         <f aca="false">B7+B22*0.5</f>
         <v>0</v>
       </c>
     </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A33" s="20" t="s">
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="21" t="s">
         <v>312</v>
       </c>
-      <c r="B33" s="27" t="n">
+      <c r="B33" s="28" t="n">
         <f aca="false">B32-B31</f>
         <v>0</v>
       </c>
     </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="20" t="s">
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="21" t="s">
         <v>313</v>
       </c>
-      <c r="B34" s="27" t="n">
+      <c r="B34" s="28" t="n">
         <f aca="false">B29-B31-B33</f>
         <v>0</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="20" t="s">
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="21" t="s">
         <v>314</v>
       </c>
-      <c r="B35" s="24" t="n">
+      <c r="B35" s="25" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="20" t="s">
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="21" t="s">
         <v>209</v>
       </c>
-      <c r="B36" s="33" t="str">
+      <c r="B36" s="34" t="str">
         <f aca="false">IF(B29=0,"",B35/B29)</f>
         <v/>
       </c>
     </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="18" t="s">
+    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="19" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="20" t="s">
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="21" t="s">
         <v>315</v>
       </c>
-      <c r="B39" s="30" t="str">
+      <c r="B39" s="31" t="str">
         <f aca="false">IF(B10=0,"AVVIK: fyll inn budsjettert salg i B10 før du leser av noe annet",IF(B29&lt;=0,"AVVIK: kapitalbehovet er null — fyll inn investeringene og forutsetningene","OK — arket regner på dine egne tall"))</f>
         <v>AVVIK: fyll inn budsjettert salg i B10 før du leser av noe annet</v>
       </c>
     </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="17" t="s">
+    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="18" t="s">
         <v>316</v>
       </c>
     </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="20" t="s">
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="21" t="s">
         <v>317</v>
       </c>
-      <c r="B41" s="30" t="str">
+      <c r="B41" s="31" t="str">
         <f aca="false">IF(ABS(B31+B33+B34-B29)&lt;1,"OK — finansieringen dekker kapitalbehovet","AVVIK: finansieringsplanen summerer seg ikke til kapitalbehovet")</f>
         <v>OK — finansieringen dekker kapitalbehovet</v>
       </c>
     </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="17" t="s">
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="18" t="s">
         <v>318</v>
       </c>
     </row>

--- a/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Regneark_Kapitalbehov.xlsx
+++ b/pensum/ok06/OK06_Kapitalbehov_og_finansiering_Regneark_Kapitalbehov.xlsx
@@ -1192,7 +1192,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1347,6 +1347,10 @@
     </xf>
     <xf numFmtId="170" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment wrapText="true" horizontal="general" vertical="bottom" textRotation="0" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1670,7 +1674,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row ht="27" customHeight="true" r="8" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="s">
         <v>9</v>
       </c>
@@ -2084,8 +2088,8 @@
         <v>81</v>
       </c>
     </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="21" t="s">
+    <row ht="27" customHeight="true" r="32" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A32" t="s">
         <v>82</v>
       </c>
       <c r="B32" s="23" t="s">
@@ -2117,8 +2121,8 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="21" t="s">
+    <row ht="27" customHeight="true" r="35" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A35" t="s">
         <v>88</v>
       </c>
       <c r="B35" s="23" t="s">
@@ -2628,8 +2632,8 @@
         <v>360</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="21" t="s">
+    <row ht="27" customHeight="true" r="7" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A7" t="s">
         <v>160</v>
       </c>
       <c r="B7" s="28" t="n">
@@ -2995,8 +2999,8 @@
         <v>188</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="21" t="s">
+    <row ht="27" customHeight="true" r="6" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A6" t="s">
         <v>189</v>
       </c>
       <c r="B6" s="27" t="n">
@@ -3287,8 +3291,8 @@
         <v>OK — eiendeler er lik egenkapital og gjeld</v>
       </c>
     </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="21" t="s">
+    <row ht="27" customHeight="true" r="37" customFormat="false" hidden="false" outlineLevel="0" collapsed="false">
+      <c s="39" r="A37" t="s">
         <v>226</v>
       </c>
       <c r="B37" s="31" t="str">
